--- a/doc/NOTES.xlsx
+++ b/doc/NOTES.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MY PC\Documents\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C0AA802-22EA-4B66-A022-3228562DC01B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C68710CA-F815-4B3B-A6E5-1D29F4FCB42B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1101" uniqueCount="964">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1148" uniqueCount="1011">
   <si>
     <t>HTML</t>
   </si>
@@ -5928,13 +5928,154 @@
   </si>
   <si>
     <t>Header,Footer, Navbar , Sidebar ,Buttons , Cards , Loaders , Popups ,paging , toaster , forms ,Dropdown , Tooltip</t>
+  </si>
+  <si>
+    <t>Transform and Transitions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                                                                       Transition Timing Function Types</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Slow start, fast middle, slow end</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slow start  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Slow start and end  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">cubic-bazier   </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Custom control curve  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">linear   </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Constant speed  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ease     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ease-in    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ease-out </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ease-in-out   </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Slow end  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">                                 Transform Function Types </t>
+  </si>
+  <si>
+    <t>matrix(scalex(), skewx(), skewx(), scaley(), translatex(), translatey())</t>
+  </si>
+  <si>
+    <t xml:space="preserve">translate(x,y)   </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Moves element  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">rotate(deg) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Rotates element  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">skew(x,y)   </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Slanks the element  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">scale(x)   </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Enlarges or shrinks  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">matrix(...)   </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Applies all of once via matrix  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3d transform </t>
+  </si>
+  <si>
+    <t xml:space="preserve">matrix3d()   </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Defines a 3D transformation, using a 4x4 matrix of 16 values  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">translate3d()      </t>
+  </si>
+  <si>
+    <t>Defines a 3D translation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">translate2()   </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Defines a 3D translation, using only the value for the Z-axis  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">scale3d()   </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Defines a 3D scale transformation  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">scale2()   </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Defines a 3D scale transformation by giving a value for the Z-axis  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">rotate3d()   </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Defines a 3D rotation  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">rotatex()   </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Defines a 3D rotation along the X-axis  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">rotatey()   </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Defines a 3D rotation along the Y-axis  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">rotateZ()   </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Defines a 3D rotation along the Z-axis  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">perspective()   </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Defines a perspective view for a 3D transformed element </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="44">
+  <fonts count="48">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -6232,6 +6373,32 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="6"/>
+      <color rgb="FF494949"/>
+      <name val="Courier New"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF494949"/>
+      <name val="Courier New"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF494949"/>
+      <name val="Courier New"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF494949"/>
+      <name val="Courier New"/>
+      <family val="3"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -6372,7 +6539,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="95">
+  <cellXfs count="99">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -6576,6 +6743,18 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="42" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -7327,7 +7506,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="B8:D669"/>
+  <dimension ref="B8:D701"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="3" max="3" width="29.81640625" customWidth="1"/>
@@ -10851,6 +11030,217 @@
     <row r="669" spans="2:4">
       <c r="D669" s="94" t="s">
         <v>962</v>
+      </c>
+    </row>
+    <row r="671" spans="2:4">
+      <c r="B671">
+        <v>91</v>
+      </c>
+      <c r="C671" t="s">
+        <v>964</v>
+      </c>
+    </row>
+    <row r="672" spans="2:4">
+      <c r="D672" t="s">
+        <v>965</v>
+      </c>
+    </row>
+    <row r="673" spans="3:4">
+      <c r="C673" s="96"/>
+    </row>
+    <row r="674" spans="3:4">
+      <c r="C674" s="97" t="s">
+        <v>973</v>
+      </c>
+      <c r="D674" t="s">
+        <v>966</v>
+      </c>
+    </row>
+    <row r="675" spans="3:4">
+      <c r="C675" s="97" t="s">
+        <v>974</v>
+      </c>
+      <c r="D675" t="s">
+        <v>967</v>
+      </c>
+    </row>
+    <row r="676" spans="3:4">
+      <c r="C676" s="97" t="s">
+        <v>975</v>
+      </c>
+      <c r="D676" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="677" spans="3:4">
+      <c r="C677" s="97" t="s">
+        <v>976</v>
+      </c>
+      <c r="D677" t="s">
+        <v>968</v>
+      </c>
+    </row>
+    <row r="678" spans="3:4">
+      <c r="C678" s="97" t="s">
+        <v>971</v>
+      </c>
+      <c r="D678" t="s">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="679" spans="3:4">
+      <c r="C679" s="97" t="s">
+        <v>969</v>
+      </c>
+      <c r="D679" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="681" spans="3:4">
+      <c r="C681" s="95"/>
+      <c r="D681" s="97" t="s">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="682" spans="3:4">
+      <c r="C682" s="95"/>
+      <c r="D682" s="97"/>
+    </row>
+    <row r="683" spans="3:4">
+      <c r="C683" s="97" t="s">
+        <v>980</v>
+      </c>
+      <c r="D683" t="s">
+        <v>981</v>
+      </c>
+    </row>
+    <row r="684" spans="3:4">
+      <c r="C684" s="97" t="s">
+        <v>982</v>
+      </c>
+      <c r="D684" t="s">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="685" spans="3:4">
+      <c r="C685" s="97" t="s">
+        <v>986</v>
+      </c>
+      <c r="D685" t="s">
+        <v>987</v>
+      </c>
+    </row>
+    <row r="686" spans="3:4">
+      <c r="C686" s="97" t="s">
+        <v>984</v>
+      </c>
+      <c r="D686" t="s">
+        <v>985</v>
+      </c>
+    </row>
+    <row r="687" spans="3:4">
+      <c r="C687" s="97" t="s">
+        <v>988</v>
+      </c>
+      <c r="D687" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="688" spans="3:4">
+      <c r="C688" s="5"/>
+      <c r="D688" t="s">
+        <v>979</v>
+      </c>
+    </row>
+    <row r="689" spans="2:4">
+      <c r="C689" s="95"/>
+    </row>
+    <row r="690" spans="2:4" ht="15">
+      <c r="B690">
+        <v>92</v>
+      </c>
+      <c r="C690" s="98" t="s">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="692" spans="2:4">
+      <c r="C692" s="97" t="s">
+        <v>991</v>
+      </c>
+      <c r="D692" t="s">
+        <v>992</v>
+      </c>
+    </row>
+    <row r="693" spans="2:4">
+      <c r="C693" s="97" t="s">
+        <v>993</v>
+      </c>
+      <c r="D693" t="s">
+        <v>994</v>
+      </c>
+    </row>
+    <row r="694" spans="2:4">
+      <c r="C694" s="97" t="s">
+        <v>995</v>
+      </c>
+      <c r="D694" t="s">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="695" spans="2:4">
+      <c r="C695" s="97" t="s">
+        <v>997</v>
+      </c>
+      <c r="D695" t="s">
+        <v>998</v>
+      </c>
+    </row>
+    <row r="696" spans="2:4">
+      <c r="C696" s="97" t="s">
+        <v>999</v>
+      </c>
+      <c r="D696" t="s">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="697" spans="2:4">
+      <c r="C697" s="97" t="s">
+        <v>1001</v>
+      </c>
+      <c r="D697" t="s">
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="698" spans="2:4">
+      <c r="C698" s="97" t="s">
+        <v>1003</v>
+      </c>
+      <c r="D698" t="s">
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="699" spans="2:4">
+      <c r="C699" s="97" t="s">
+        <v>1005</v>
+      </c>
+      <c r="D699" t="s">
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="700" spans="2:4">
+      <c r="C700" s="97" t="s">
+        <v>1007</v>
+      </c>
+      <c r="D700" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="701" spans="2:4">
+      <c r="C701" s="97" t="s">
+        <v>1009</v>
+      </c>
+      <c r="D701" t="s">
+        <v>1010</v>
       </c>
     </row>
   </sheetData>
